--- a/backend/data/financials_by_company/0176.HK.xlsx
+++ b/backend/data/financials_by_company/0176.HK.xlsx
@@ -657,135 +657,143 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-2794487.310474</v>
+        <v>-15135120</v>
       </c>
       <c r="C2" t="n">
-        <v>0.017765</v>
+        <v>0.165</v>
       </c>
       <c r="D2" t="n">
-        <v>15030000</v>
+        <v>16636000</v>
       </c>
       <c r="E2" t="n">
-        <v>-157300000</v>
+        <v>-91728000</v>
       </c>
       <c r="F2" t="n">
-        <v>-157300000</v>
+        <v>-91728000</v>
       </c>
       <c r="G2" t="n">
-        <v>-239044000</v>
+        <v>-144126000</v>
       </c>
       <c r="H2" t="n">
-        <v>23579000</v>
+        <v>22607000</v>
       </c>
       <c r="I2" t="n">
-        <v>46717000</v>
+        <v>83215000</v>
       </c>
       <c r="J2" t="n">
-        <v>-142270000</v>
+        <v>-75092000</v>
       </c>
       <c r="K2" t="n">
-        <v>-165849000</v>
+        <v>-97699000</v>
       </c>
       <c r="L2" t="n">
-        <v>-78832000</v>
+        <v>-24628000</v>
       </c>
       <c r="M2" t="n">
-        <v>78841000</v>
+        <v>24643000</v>
       </c>
       <c r="N2" t="n">
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="O2" t="n">
-        <v>-84538487.31047399</v>
+        <v>-67533120</v>
       </c>
       <c r="P2" t="n">
-        <v>-239044000</v>
+        <v>-144126000</v>
       </c>
       <c r="Q2" t="n">
-        <v>101899000</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
+        <v>138719000</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2032571385</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2032571385</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-0.0709</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.0709</v>
+      </c>
       <c r="V2" t="n">
-        <v>-239044000</v>
+        <v>-144126000</v>
       </c>
       <c r="W2" t="n">
-        <v>-239044000</v>
+        <v>-144126000</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-239044000</v>
+        <v>-144126000</v>
       </c>
       <c r="Z2" t="n">
-        <v>1299000</v>
+        <v>-439000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-240343000</v>
+        <v>-143687000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-240343000</v>
+        <v>-143687000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-4347000</v>
+        <v>21345000</v>
       </c>
       <c r="AD2" t="n">
-        <v>-244690000</v>
+        <v>-122342000</v>
       </c>
       <c r="AE2" t="n">
-        <v>4550000</v>
+        <v>6034000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-151251000</v>
+        <v>-93428000</v>
       </c>
       <c r="AG2" t="inlineStr"/>
       <c r="AH2" t="n">
-        <v>-830000</v>
+        <v>85203000</v>
       </c>
       <c r="AI2" t="n">
-        <v>152081000</v>
+        <v>8225000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-78832000</v>
+        <v>-24628000</v>
       </c>
       <c r="AK2" t="n">
-        <v>78841000</v>
+        <v>24643000</v>
       </c>
       <c r="AL2" t="n">
-        <v>9000</v>
+        <v>15000</v>
       </c>
       <c r="AM2" t="n">
-        <v>-34265000</v>
+        <v>-6502000</v>
       </c>
       <c r="AN2" t="n">
-        <v>55182000</v>
+        <v>55504000</v>
       </c>
       <c r="AO2" t="n">
-        <v>56754000</v>
+        <v>57896000</v>
       </c>
       <c r="AP2" t="n">
-        <v>1178000</v>
+        <v>1406000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>55576000</v>
+        <v>56490000</v>
       </c>
       <c r="AR2" t="n">
-        <v>20917000</v>
+        <v>49002000</v>
       </c>
       <c r="AS2" t="n">
-        <v>46717000</v>
+        <v>83215000</v>
       </c>
       <c r="AT2" t="n">
-        <v>67634000</v>
+        <v>132217000</v>
       </c>
       <c r="AU2" t="n">
-        <v>67634000</v>
+        <v>132217000</v>
       </c>
     </row>
     <row r="3">
@@ -933,143 +941,135 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-15135120</v>
+        <v>-2794487.310474</v>
       </c>
       <c r="C4" t="n">
-        <v>0.165</v>
+        <v>0.017765</v>
       </c>
       <c r="D4" t="n">
-        <v>16636000</v>
+        <v>15030000</v>
       </c>
       <c r="E4" t="n">
-        <v>-91728000</v>
+        <v>-157300000</v>
       </c>
       <c r="F4" t="n">
-        <v>-91728000</v>
+        <v>-157300000</v>
       </c>
       <c r="G4" t="n">
-        <v>-144126000</v>
+        <v>-239044000</v>
       </c>
       <c r="H4" t="n">
-        <v>22607000</v>
+        <v>23579000</v>
       </c>
       <c r="I4" t="n">
-        <v>83215000</v>
+        <v>46717000</v>
       </c>
       <c r="J4" t="n">
-        <v>-75092000</v>
+        <v>-142270000</v>
       </c>
       <c r="K4" t="n">
-        <v>-97699000</v>
+        <v>-165849000</v>
       </c>
       <c r="L4" t="n">
-        <v>-24628000</v>
+        <v>-78832000</v>
       </c>
       <c r="M4" t="n">
-        <v>24643000</v>
+        <v>78841000</v>
       </c>
       <c r="N4" t="n">
-        <v>15000</v>
+        <v>9000</v>
       </c>
       <c r="O4" t="n">
-        <v>-67533120</v>
+        <v>-84538487.31047399</v>
       </c>
       <c r="P4" t="n">
-        <v>-144126000</v>
+        <v>-239044000</v>
       </c>
       <c r="Q4" t="n">
-        <v>138719000</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2032571385</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2032571385</v>
-      </c>
-      <c r="T4" t="n">
-        <v>-0.0709</v>
-      </c>
-      <c r="U4" t="n">
-        <v>-0.0709</v>
-      </c>
+        <v>101899000</v>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-144126000</v>
+        <v>-239044000</v>
       </c>
       <c r="W4" t="n">
-        <v>-144126000</v>
+        <v>-239044000</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>-144126000</v>
+        <v>-239044000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-439000</v>
+        <v>1299000</v>
       </c>
       <c r="AA4" t="n">
-        <v>-143687000</v>
+        <v>-240343000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-143687000</v>
+        <v>-240343000</v>
       </c>
       <c r="AC4" t="n">
-        <v>21345000</v>
+        <v>-4347000</v>
       </c>
       <c r="AD4" t="n">
-        <v>-122342000</v>
+        <v>-244690000</v>
       </c>
       <c r="AE4" t="n">
-        <v>6034000</v>
+        <v>4550000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-93428000</v>
+        <v>-151251000</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>85203000</v>
+        <v>-830000</v>
       </c>
       <c r="AI4" t="n">
-        <v>8225000</v>
+        <v>152081000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-24628000</v>
+        <v>-78832000</v>
       </c>
       <c r="AK4" t="n">
-        <v>24643000</v>
+        <v>78841000</v>
       </c>
       <c r="AL4" t="n">
-        <v>15000</v>
+        <v>9000</v>
       </c>
       <c r="AM4" t="n">
-        <v>-6502000</v>
+        <v>-34265000</v>
       </c>
       <c r="AN4" t="n">
-        <v>55504000</v>
+        <v>55182000</v>
       </c>
       <c r="AO4" t="n">
-        <v>57896000</v>
+        <v>56754000</v>
       </c>
       <c r="AP4" t="n">
-        <v>1406000</v>
+        <v>1178000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>56490000</v>
+        <v>55576000</v>
       </c>
       <c r="AR4" t="n">
-        <v>49002000</v>
+        <v>20917000</v>
       </c>
       <c r="AS4" t="n">
-        <v>83215000</v>
+        <v>46717000</v>
       </c>
       <c r="AT4" t="n">
-        <v>132217000</v>
+        <v>67634000</v>
       </c>
       <c r="AU4" t="n">
-        <v>132217000</v>
+        <v>67634000</v>
       </c>
     </row>
   </sheetData>
@@ -1430,7 +1430,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
         <v>2032571385</v>
@@ -1439,43 +1439,43 @@
         <v>2032571385</v>
       </c>
       <c r="D2" t="n">
-        <v>478977000</v>
+        <v>492898000</v>
       </c>
       <c r="E2" t="n">
-        <v>484867000</v>
+        <v>498771000</v>
       </c>
       <c r="F2" t="n">
-        <v>29440000</v>
+        <v>403601000</v>
       </c>
       <c r="G2" t="n">
-        <v>520199000</v>
+        <v>914548000</v>
       </c>
       <c r="H2" t="n">
-        <v>-263792000</v>
+        <v>192757000</v>
       </c>
       <c r="I2" t="n">
-        <v>29440000</v>
+        <v>403601000</v>
       </c>
       <c r="J2" t="n">
-        <v>81000</v>
+        <v>187000</v>
       </c>
       <c r="K2" t="n">
-        <v>35413000</v>
+        <v>415964000</v>
       </c>
       <c r="L2" t="n">
-        <v>37386000</v>
+        <v>647019000</v>
       </c>
       <c r="M2" t="n">
-        <v>44336000</v>
+        <v>427150000</v>
       </c>
       <c r="N2" t="n">
-        <v>8923000</v>
+        <v>11186000</v>
       </c>
       <c r="O2" t="n">
-        <v>35413000</v>
+        <v>415964000</v>
       </c>
       <c r="P2" t="n">
-        <v>-659784000</v>
+        <v>-327314000</v>
       </c>
       <c r="Q2" t="n">
         <v>478431000</v>
@@ -1487,96 +1487,98 @@
         <v>203257000</v>
       </c>
       <c r="T2" t="n">
-        <v>865087000</v>
+        <v>828267000</v>
       </c>
       <c r="U2" t="n">
-        <v>2297000</v>
+        <v>232486000</v>
       </c>
       <c r="V2" t="n">
-        <v>300000</v>
+        <v>1296000</v>
       </c>
       <c r="W2" t="n">
-        <v>1997000</v>
+        <v>231190000</v>
       </c>
       <c r="X2" t="n">
-        <v>24000</v>
+        <v>135000</v>
       </c>
       <c r="Y2" t="n">
-        <v>1973000</v>
+        <v>231055000</v>
       </c>
       <c r="Z2" t="n">
-        <v>862790000</v>
-      </c>
-      <c r="AA2" t="inlineStr"/>
+        <v>595781000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2395000</v>
+      </c>
       <c r="AB2" t="n">
-        <v>482870000</v>
+        <v>267581000</v>
       </c>
       <c r="AC2" t="n">
-        <v>57000</v>
+        <v>52000</v>
       </c>
       <c r="AD2" t="n">
-        <v>482813000</v>
+        <v>267529000</v>
       </c>
       <c r="AE2" t="n">
-        <v>50430000</v>
+        <v>142735000</v>
       </c>
       <c r="AF2" t="n">
-        <v>5068000</v>
+        <v>84754000</v>
       </c>
       <c r="AG2" t="n">
-        <v>18732000</v>
+        <v>32116000</v>
       </c>
       <c r="AH2" t="n">
-        <v>26630000</v>
+        <v>25865000</v>
       </c>
       <c r="AI2" t="n">
-        <v>909423000</v>
+        <v>1255417000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>310425000</v>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+        <v>466879000</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1000</v>
+      </c>
       <c r="AL2" t="n">
-        <v>59000000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>59000000</v>
-      </c>
+        <v>8720000</v>
+      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>8720000</v>
       </c>
       <c r="AO2" t="n">
-        <v>556000</v>
+        <v>146313000</v>
       </c>
       <c r="AP2" t="n">
-        <v>556000</v>
+        <v>146313000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5973000</v>
+        <v>12363000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1825000</v>
+        <v>7857000</v>
       </c>
       <c r="AS2" t="n">
-        <v>4148000</v>
+        <v>4506000</v>
       </c>
       <c r="AT2" t="n">
-        <v>244896000</v>
+        <v>299483000</v>
       </c>
       <c r="AU2" t="n">
-        <v>-141512000</v>
+        <v>-86705000</v>
       </c>
       <c r="AV2" t="n">
-        <v>386408000</v>
+        <v>386188000</v>
       </c>
       <c r="AW2" t="n">
-        <v>1839000</v>
+        <v>2022000</v>
       </c>
       <c r="AX2" t="n">
-        <v>18353000</v>
+        <v>16276000</v>
       </c>
       <c r="AY2" t="n">
-        <v>18553000</v>
+        <v>20227000</v>
       </c>
       <c r="AZ2" t="n">
         <v>347663000</v>
@@ -1585,50 +1587,52 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>598998000</v>
+        <v>788538000</v>
       </c>
       <c r="BC2" t="n">
-        <v>539519000</v>
+        <v>602664000</v>
       </c>
       <c r="BD2" t="n">
-        <v>227000</v>
-      </c>
-      <c r="BE2" t="inlineStr"/>
+        <v>1890000</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>11575000</v>
+      </c>
       <c r="BF2" t="n">
-        <v>18854000</v>
+        <v>8765000</v>
       </c>
       <c r="BG2" t="n">
-        <v>306000</v>
+        <v>2208000</v>
       </c>
       <c r="BH2" t="n">
-        <v>4546000</v>
+        <v>1456000</v>
       </c>
       <c r="BI2" t="n">
-        <v>14002000</v>
+        <v>5101000</v>
       </c>
       <c r="BJ2" t="n">
-        <v>19205000</v>
+        <v>125969000</v>
       </c>
       <c r="BK2" t="n">
-        <v>0</v>
+        <v>804000</v>
       </c>
       <c r="BL2" t="n">
-        <v>15384000</v>
+        <v>42760000</v>
       </c>
       <c r="BM2" t="n">
-        <v>-205000</v>
+        <v>-11530000</v>
       </c>
       <c r="BN2" t="n">
-        <v>15589000</v>
+        <v>54290000</v>
       </c>
       <c r="BO2" t="n">
-        <v>5809000</v>
+        <v>5686000</v>
       </c>
       <c r="BP2" t="n">
-        <v>5809000</v>
+        <v>5686000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>5809000</v>
+        <v>5686000</v>
       </c>
     </row>
     <row r="3">
@@ -1838,7 +1842,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>2032571385</v>
@@ -1847,43 +1851,43 @@
         <v>2032571385</v>
       </c>
       <c r="D4" t="n">
-        <v>492898000</v>
+        <v>478977000</v>
       </c>
       <c r="E4" t="n">
-        <v>498771000</v>
+        <v>484867000</v>
       </c>
       <c r="F4" t="n">
-        <v>403601000</v>
+        <v>29440000</v>
       </c>
       <c r="G4" t="n">
-        <v>914548000</v>
+        <v>520199000</v>
       </c>
       <c r="H4" t="n">
-        <v>192757000</v>
+        <v>-263792000</v>
       </c>
       <c r="I4" t="n">
-        <v>403601000</v>
+        <v>29440000</v>
       </c>
       <c r="J4" t="n">
-        <v>187000</v>
+        <v>81000</v>
       </c>
       <c r="K4" t="n">
-        <v>415964000</v>
+        <v>35413000</v>
       </c>
       <c r="L4" t="n">
-        <v>647019000</v>
+        <v>37386000</v>
       </c>
       <c r="M4" t="n">
-        <v>427150000</v>
+        <v>44336000</v>
       </c>
       <c r="N4" t="n">
-        <v>11186000</v>
+        <v>8923000</v>
       </c>
       <c r="O4" t="n">
-        <v>415964000</v>
+        <v>35413000</v>
       </c>
       <c r="P4" t="n">
-        <v>-327314000</v>
+        <v>-659784000</v>
       </c>
       <c r="Q4" t="n">
         <v>478431000</v>
@@ -1895,98 +1899,96 @@
         <v>203257000</v>
       </c>
       <c r="T4" t="n">
-        <v>828267000</v>
+        <v>865087000</v>
       </c>
       <c r="U4" t="n">
-        <v>232486000</v>
+        <v>2297000</v>
       </c>
       <c r="V4" t="n">
-        <v>1296000</v>
+        <v>300000</v>
       </c>
       <c r="W4" t="n">
-        <v>231190000</v>
+        <v>1997000</v>
       </c>
       <c r="X4" t="n">
-        <v>135000</v>
+        <v>24000</v>
       </c>
       <c r="Y4" t="n">
-        <v>231055000</v>
+        <v>1973000</v>
       </c>
       <c r="Z4" t="n">
-        <v>595781000</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2395000</v>
-      </c>
+        <v>862790000</v>
+      </c>
+      <c r="AA4" t="inlineStr"/>
       <c r="AB4" t="n">
-        <v>267581000</v>
+        <v>482870000</v>
       </c>
       <c r="AC4" t="n">
-        <v>52000</v>
+        <v>57000</v>
       </c>
       <c r="AD4" t="n">
-        <v>267529000</v>
+        <v>482813000</v>
       </c>
       <c r="AE4" t="n">
-        <v>142735000</v>
+        <v>50430000</v>
       </c>
       <c r="AF4" t="n">
-        <v>84754000</v>
+        <v>5068000</v>
       </c>
       <c r="AG4" t="n">
-        <v>32116000</v>
+        <v>18732000</v>
       </c>
       <c r="AH4" t="n">
-        <v>25865000</v>
+        <v>26630000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1255417000</v>
+        <v>909423000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>466879000</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1000</v>
-      </c>
+        <v>310425000</v>
+      </c>
+      <c r="AK4" t="inlineStr"/>
       <c r="AL4" t="n">
-        <v>8720000</v>
-      </c>
-      <c r="AM4" t="inlineStr"/>
+        <v>59000000</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>59000000</v>
+      </c>
       <c r="AN4" t="n">
-        <v>8720000</v>
+        <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>146313000</v>
+        <v>556000</v>
       </c>
       <c r="AP4" t="n">
-        <v>146313000</v>
+        <v>556000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12363000</v>
+        <v>5973000</v>
       </c>
       <c r="AR4" t="n">
-        <v>7857000</v>
+        <v>1825000</v>
       </c>
       <c r="AS4" t="n">
-        <v>4506000</v>
+        <v>4148000</v>
       </c>
       <c r="AT4" t="n">
-        <v>299483000</v>
+        <v>244896000</v>
       </c>
       <c r="AU4" t="n">
-        <v>-86705000</v>
+        <v>-141512000</v>
       </c>
       <c r="AV4" t="n">
-        <v>386188000</v>
+        <v>386408000</v>
       </c>
       <c r="AW4" t="n">
-        <v>2022000</v>
+        <v>1839000</v>
       </c>
       <c r="AX4" t="n">
-        <v>16276000</v>
+        <v>18353000</v>
       </c>
       <c r="AY4" t="n">
-        <v>20227000</v>
+        <v>18553000</v>
       </c>
       <c r="AZ4" t="n">
         <v>347663000</v>
@@ -1995,52 +1997,50 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>788538000</v>
+        <v>598998000</v>
       </c>
       <c r="BC4" t="n">
-        <v>602664000</v>
+        <v>539519000</v>
       </c>
       <c r="BD4" t="n">
-        <v>1890000</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>11575000</v>
-      </c>
+        <v>227000</v>
+      </c>
+      <c r="BE4" t="inlineStr"/>
       <c r="BF4" t="n">
-        <v>8765000</v>
+        <v>18854000</v>
       </c>
       <c r="BG4" t="n">
-        <v>2208000</v>
+        <v>306000</v>
       </c>
       <c r="BH4" t="n">
-        <v>1456000</v>
+        <v>4546000</v>
       </c>
       <c r="BI4" t="n">
-        <v>5101000</v>
+        <v>14002000</v>
       </c>
       <c r="BJ4" t="n">
-        <v>125969000</v>
+        <v>19205000</v>
       </c>
       <c r="BK4" t="n">
-        <v>804000</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>42760000</v>
+        <v>15384000</v>
       </c>
       <c r="BM4" t="n">
-        <v>-11530000</v>
+        <v>-205000</v>
       </c>
       <c r="BN4" t="n">
-        <v>54290000</v>
+        <v>15589000</v>
       </c>
       <c r="BO4" t="n">
-        <v>5686000</v>
+        <v>5809000</v>
       </c>
       <c r="BP4" t="n">
-        <v>5686000</v>
+        <v>5809000</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5686000</v>
+        <v>5809000</v>
       </c>
     </row>
   </sheetData>
@@ -2276,120 +2276,134 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45291</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>3822000</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>29960000</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-16923000</v>
+      </c>
       <c r="D2" t="n">
-        <v>-6609000</v>
+        <v>-18397000</v>
       </c>
       <c r="E2" t="n">
-        <v>4604000</v>
+        <v>18000000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1017000</v>
+        <v>-4601000</v>
       </c>
       <c r="G2" t="n">
-        <v>5809000</v>
+        <v>5686000</v>
       </c>
       <c r="H2" t="n">
-        <v>8365000</v>
+        <v>11598000</v>
       </c>
       <c r="I2" t="n">
-        <v>-113000</v>
+        <v>-363000</v>
       </c>
       <c r="J2" t="n">
-        <v>-2443000</v>
+        <v>-5549000</v>
       </c>
       <c r="K2" t="n">
-        <v>-9039000</v>
+        <v>-35524000</v>
       </c>
       <c r="L2" t="n">
-        <v>2199000</v>
+        <v>-2894000</v>
       </c>
       <c r="M2" t="n">
-        <v>-9179000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
+        <v>-15034000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-16923000</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-16923000</v>
+      </c>
       <c r="P2" t="n">
-        <v>-2005000</v>
+        <v>-397000</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2005000</v>
+        <v>-397000</v>
       </c>
       <c r="R2" t="n">
-        <v>-6609000</v>
+        <v>-18397000</v>
       </c>
       <c r="S2" t="n">
-        <v>4604000</v>
+        <v>18000000</v>
       </c>
       <c r="T2" t="n">
-        <v>1757000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>2767000</v>
-      </c>
+        <v>-4586000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>7000</v>
-      </c>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
+        <v>15000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
       <c r="AA2" t="n">
-        <v>-1017000</v>
+        <v>-4601000</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1017000</v>
+        <v>-4601000</v>
       </c>
       <c r="AD2" t="n">
-        <v>4839000</v>
+        <v>34561000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-4233000</v>
+        <v>-3079000</v>
       </c>
       <c r="AF2" t="n">
-        <v>15206000</v>
+        <v>15501000</v>
       </c>
       <c r="AG2" t="n">
-        <v>9082000</v>
+        <v>-15769000</v>
       </c>
       <c r="AH2" t="n">
-        <v>-4701000</v>
+        <v>24561000</v>
       </c>
       <c r="AI2" t="n">
-        <v>-5130000</v>
+        <v>-3011000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>15955000</v>
+        <v>9720000</v>
       </c>
       <c r="AK2" t="n">
-        <v>78834000</v>
+        <v>24628000</v>
       </c>
       <c r="AL2" t="n">
-        <v>23579000</v>
+        <v>22607000</v>
       </c>
       <c r="AM2" t="n">
-        <v>23579000</v>
+        <v>22607000</v>
       </c>
       <c r="AN2" t="n">
-        <v>6049000</v>
+        <v>-1700000</v>
       </c>
       <c r="AO2" t="n">
-        <v>-1000</v>
+        <v>5000</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
-      <c r="AQ2" t="inlineStr"/>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
       <c r="AR2" t="n">
-        <v>-244690000</v>
+        <v>-122342000</v>
       </c>
     </row>
     <row r="3">
@@ -2518,134 +2532,120 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>29960000</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-16923000</v>
-      </c>
+        <v>3822000</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="n">
-        <v>-18397000</v>
+        <v>-6609000</v>
       </c>
       <c r="E4" t="n">
-        <v>18000000</v>
+        <v>4604000</v>
       </c>
       <c r="F4" t="n">
-        <v>-4601000</v>
+        <v>-1017000</v>
       </c>
       <c r="G4" t="n">
-        <v>5686000</v>
+        <v>5809000</v>
       </c>
       <c r="H4" t="n">
-        <v>11598000</v>
+        <v>8365000</v>
       </c>
       <c r="I4" t="n">
-        <v>-363000</v>
+        <v>-113000</v>
       </c>
       <c r="J4" t="n">
-        <v>-5549000</v>
+        <v>-2443000</v>
       </c>
       <c r="K4" t="n">
-        <v>-35524000</v>
+        <v>-9039000</v>
       </c>
       <c r="L4" t="n">
-        <v>-2894000</v>
+        <v>2199000</v>
       </c>
       <c r="M4" t="n">
-        <v>-15034000</v>
-      </c>
-      <c r="N4" t="n">
-        <v>-16923000</v>
-      </c>
-      <c r="O4" t="n">
-        <v>-16923000</v>
-      </c>
+        <v>-9179000</v>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
-        <v>-397000</v>
+        <v>-2005000</v>
       </c>
       <c r="Q4" t="n">
-        <v>-397000</v>
+        <v>-2005000</v>
       </c>
       <c r="R4" t="n">
-        <v>-18397000</v>
+        <v>-6609000</v>
       </c>
       <c r="S4" t="n">
-        <v>18000000</v>
+        <v>4604000</v>
       </c>
       <c r="T4" t="n">
-        <v>-4586000</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>1757000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2767000</v>
+      </c>
       <c r="V4" t="n">
-        <v>15000</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
+        <v>7000</v>
+      </c>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="n">
-        <v>-4601000</v>
+        <v>-1017000</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4601000</v>
+        <v>-1017000</v>
       </c>
       <c r="AD4" t="n">
-        <v>34561000</v>
+        <v>4839000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-3079000</v>
+        <v>-4233000</v>
       </c>
       <c r="AF4" t="n">
-        <v>15501000</v>
+        <v>15206000</v>
       </c>
       <c r="AG4" t="n">
-        <v>-15769000</v>
+        <v>9082000</v>
       </c>
       <c r="AH4" t="n">
-        <v>24561000</v>
+        <v>-4701000</v>
       </c>
       <c r="AI4" t="n">
-        <v>-3011000</v>
+        <v>-5130000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>9720000</v>
+        <v>15955000</v>
       </c>
       <c r="AK4" t="n">
-        <v>24628000</v>
+        <v>78834000</v>
       </c>
       <c r="AL4" t="n">
-        <v>22607000</v>
+        <v>23579000</v>
       </c>
       <c r="AM4" t="n">
-        <v>22607000</v>
+        <v>23579000</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1700000</v>
+        <v>6049000</v>
       </c>
       <c r="AO4" t="n">
-        <v>5000</v>
+        <v>-1000</v>
       </c>
       <c r="AP4" t="n">
         <v>0</v>
       </c>
-      <c r="AQ4" t="n">
-        <v>0</v>
-      </c>
+      <c r="AQ4" t="inlineStr"/>
       <c r="AR4" t="n">
-        <v>-122342000</v>
+        <v>-244690000</v>
       </c>
     </row>
   </sheetData>
@@ -3180,192 +3180,192 @@
       </c>
       <c r="CZ1" t="inlineStr">
         <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DM1" t="inlineStr">
+        <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DA1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DB1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DC1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DD1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DE1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DF1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DG1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DH1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="DL1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="DY1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EB1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>priceToBook</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="EJ1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="DW1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="DX1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DY1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EK1" t="inlineStr">
         <is>
           <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>marketState</t>
         </is>
       </c>
       <c r="EL1" t="inlineStr">
@@ -3377,17 +3377,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Shun Tak Centre, West Tower</t>
+          <t>Siu On Centre</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Room 1510, 15th Floor 168-200 Connaught Road Central Sheung Wan</t>
+          <t>Room 903, 9th Floor 188 Lockhart Road</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>Wanchai</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -3442,7 +3442,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Superactive Group Company Limited, an investment holding company, manufactures and sells consumer electronic products in Hong Kong and the People's Republic of China. It operates through four segments: Manufacture of Electronics Products; Money Lending Business; Property Development and Management Business; and Regulated Financial Services Business. The company also provides management services for landlords and tenants; asset management services; and develops properties. Superactive Group Company Limited was incorporated in 1994 and is headquartered in Central, Hong Kong. Superactive Group Company Limited is a subsidiary of Super Fame Holdings Limited.</t>
+          <t>Superactive Group Company Limited, an investment holding company, manufactures and sells consumer electronic products in Hong Kong and the People's Republic of China. It operates through four segments: Manufacture of Electronics Products; Money Lending Business; Property Development and Management Business; and Regulated Financial Services Business. The company also provides management services for landlords and tenants; asset management services; and develops properties. Superactive Group Company Limited was incorporated in 1994 and is headquartered in Wanchai, Hong Kong. Superactive Group Company Limited is a subsidiary of Super Fame Holdings Limited.</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -3498,7 +3498,7 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.678</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="AF2" t="n">
         <v>110000</v>
@@ -3628,7 +3628,7 @@
         <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.27294624</v>
+        <v>0.24487448</v>
       </c>
       <c r="BV2" t="n">
         <v>0.005</v>
@@ -3739,43 +3739,49 @@
         </is>
       </c>
       <c r="CZ2" t="n">
-        <v>0</v>
+        <v>1743408508</v>
       </c>
       <c r="DA2" t="inlineStr">
         <is>
-          <t>0.013 - 0.015</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="DB2" t="inlineStr">
         <is>
-          <t>HKSE</t>
-        </is>
-      </c>
-      <c r="DC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>0</v>
+          <t>finmb_418667</t>
+        </is>
+      </c>
+      <c r="DC2" t="inlineStr">
+        <is>
+          <t>Asia/Hong_Kong</t>
+        </is>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>HKT</t>
+        </is>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>28800000</v>
       </c>
       <c r="DF2" t="inlineStr">
         <is>
-          <t>0.013 - 0.015</t>
-        </is>
-      </c>
-      <c r="DG2" t="n">
-        <v>-0.0019999994</v>
+          <t>hk_market</t>
+        </is>
+      </c>
+      <c r="DG2" t="b">
+        <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>-0.1333333</v>
+        <v>0</v>
       </c>
       <c r="DI2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>1724845862</v>
+        <v>0.013</v>
+      </c>
+      <c r="DJ2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
       </c>
       <c r="DK2" t="b">
         <v>0</v>
@@ -3784,96 +3790,90 @@
         <v>946949400000</v>
       </c>
       <c r="DM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>0.013 - 0.015</t>
+        </is>
+      </c>
+      <c r="DO2" t="inlineStr">
+        <is>
+          <t>HKSE</t>
+        </is>
+      </c>
+      <c r="DP2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>0.013 - 0.015</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>-0.0019999994</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>-0.1333333</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1724845862</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>1724845862</v>
+      </c>
+      <c r="DY2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="n">
         <v>-0.13</v>
       </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DR2" t="n">
+      <c r="EA2" t="inlineStr">
+        <is>
+          <t>SUPERACTIVE GP</t>
+        </is>
+      </c>
+      <c r="EB2" t="inlineStr">
+        <is>
+          <t>Superactive Group Company Limited</t>
+        </is>
+      </c>
+      <c r="EC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EG2" t="n">
         <v>-0.8666667</v>
       </c>
-      <c r="DS2" t="n">
+      <c r="EH2" t="n">
         <v>15</v>
       </c>
-      <c r="DT2" t="n">
+      <c r="EI2" t="n">
         <v>15</v>
       </c>
-      <c r="DU2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>1724845862</v>
-      </c>
-      <c r="DW2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>0.013</v>
-      </c>
-      <c r="DZ2" t="inlineStr">
+      <c r="EJ2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EK2" t="inlineStr">
         <is>
           <t>[]</t>
-        </is>
-      </c>
-      <c r="EA2" t="n">
-        <v>1743408508</v>
-      </c>
-      <c r="EB2" t="inlineStr">
-        <is>
-          <t>HKG</t>
-        </is>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>finmb_418667</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
-        <is>
-          <t>Asia/Hong_Kong</t>
-        </is>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>HKT</t>
-        </is>
-      </c>
-      <c r="EF2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EG2" t="inlineStr">
-        <is>
-          <t>hk_market</t>
-        </is>
-      </c>
-      <c r="EH2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EI2" t="inlineStr">
-        <is>
-          <t>SUPERACTIVE GP</t>
-        </is>
-      </c>
-      <c r="EJ2" t="inlineStr">
-        <is>
-          <t>Superactive Group Company Limited</t>
-        </is>
-      </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
         </is>
       </c>
       <c r="EL2" t="inlineStr"/>
